--- a/Codelist Excel Files and Conversion Templates to XML/measurementKind.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/measurementKind.xlsx
@@ -1233,14 +1233,62 @@
         <f>IF(ISNA(VLOOKUP(B7,AssociatedElements!B$2:B2945,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="G7" s="9" t="n"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>composite_load_test</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Composite / group load test</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A load test applied to a group of inclusions together with the soil between them, measuring the response of the treated ground as a composite rather than the response of one element.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2">
         <f>IF(ISNA(VLOOKUP(B8,AssociatedElements!B$2:B2946,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="G8" s="9" t="n"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>soil_load_test</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Test on surrounding soil</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A load test applied to the soil between inclusions rather than to an inclusion, used to verify the stress and settlement assumed for the untreated soil in a composite-ground design.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2">
@@ -1708,14 +1756,32 @@
         <f>IF(ISNA(VLOOKUP(B7,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B7" s="2" t="n"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>composite_load_test</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>//diggs:TargetMeasurement/diggs:measurementKind</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
         <f>IF(ISNA(VLOOKUP(B8,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B8" s="2" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>soil_load_test</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>//diggs:TargetMeasurement/diggs:measurementKind</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9">

--- a/Codelist Excel Files and Conversion Templates to XML/measurementKind.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/measurementKind.xlsx
@@ -1292,25 +1292,66 @@
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <f>IF(ISNA(VLOOKUP(B9,AssociatedElements!B$2:B2947,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="G9" s="9" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B9,AssociatedElements!B$2:B$999,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>plate_load_test</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Plate load test</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>A plate-bearing load test on a single deep foundation element head, measuring ground or platform stiffness rather than the element's own axial capacity, per ASTM D1194 (withdrawn 2003, still in practical use), ASTM D1195/D1196, or DIN 18134.</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>ASTM D1196</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <f>IF(ISNA(VLOOKUP(B10,AssociatedElements!B$2:B2948,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="13" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B10,AssociatedElements!B$2:B$999,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>zone_load_test</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Zone load test</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>A large-plate load test on a load transfer platform over a group of columns, per BS 8006-1 (which requires the test), typically executed to ASTM D1195/D1196 or DIN 18134's methodology.</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F10" s="13" t="n"/>
-      <c r="G10" s="9" t="n"/>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>BS 8006-1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2">
@@ -1785,17 +1826,35 @@
     </row>
     <row r="9">
       <c r="A9">
-        <f>IF(ISNA(VLOOKUP(B9,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B9" s="2" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B9,Definitions!B$2:B$999,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>plate_load_test</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>//diggs:TargetMeasurement/diggs:measurementKind</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
-        <f>IF(ISNA(VLOOKUP(B10,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B10" s="20" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B10,Definitions!B$2:B$999,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>zone_load_test</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>//diggs:TargetMeasurement/diggs:measurementKind</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11">

--- a/Codelist Excel Files and Conversion Templates to XML/measurementKind.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/measurementKind.xlsx
@@ -1358,12 +1358,32 @@
         <f>IF(ISNA(VLOOKUP(B11,AssociatedElements!B$2:B2949,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="13" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>thermal_integrity_profiling</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Thermal integrity profiling</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>A thermal integrity test that relates the heat of hydration generated by curing concrete along a completed element's length to its as-built cross-section and continuity, per ASTM D7949.</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F11" s="13" t="n"/>
-      <c r="G11" s="9" t="n"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>ASTM D7949</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2">
@@ -1861,7 +1881,16 @@
         <f>IF(ISNA(VLOOKUP(B11,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B11" s="20" t="n"/>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>thermal_integrity_profiling</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>//diggs:TargetMeasurement/diggs:measurementKind</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
